--- a/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
+++ b/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\DPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB717C7-2A8A-4BEC-A558-3F2E3A1EA905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819173F8-314B-44DF-BEC5-13FEFB698E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -673,94 +673,94 @@
         <v>9</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.25">
@@ -2288,94 +2288,94 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">

--- a/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
+++ b/InputData/elec/DPbES/Dispatch Priority by Elec Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27528"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\DPbES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\elec\DPbES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{819173F8-314B-44DF-BEC5-13FEFB698E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C8F9E5-B6A6-4447-82DB-CD37DB5FC402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DPbES!$A$1:$AK$14</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -39,10 +42,46 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
+    <t>DPbES Dispatch Priority by Electricity Source</t>
+  </si>
+  <si>
+    <t>Source:</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>Use a Boolean value of 1 if the electricity source should be preferenced in guaranteed dispatch.</t>
+  </si>
+  <si>
+    <t>If the amount of guaranteed dispatch exceeds demand in a given hour, then those sources marked with</t>
+  </si>
+  <si>
+    <t>0s will be scaled back proportionately while those with a value of 1 will not be reduced.</t>
+  </si>
+  <si>
+    <t>Priority Order (dimensionless)</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
     <t>nuclear</t>
   </si>
   <si>
     <t>hydro</t>
+  </si>
+  <si>
+    <t>onshore wind</t>
   </si>
   <si>
     <t>solar PV</t>
@@ -66,16 +105,7 @@
     <t>lignite</t>
   </si>
   <si>
-    <t>hard coal</t>
-  </si>
-  <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
     <t>offshore wind</t>
-  </si>
-  <si>
-    <t>Source:</t>
   </si>
   <si>
     <t>crude oil</t>
@@ -85,15 +115,6 @@
   </si>
   <si>
     <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>Priority Order (dimensionless)</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
   </si>
   <si>
     <t>hard coal w CCS</t>
@@ -116,30 +137,12 @@
   <si>
     <t>hydrogen combined cycle</t>
   </si>
-  <si>
-    <t>DPbES Dispatch Priority by Electricity Source</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>Use a Boolean value of 1 if the electricity source should be preferenced in guaranteed dispatch.</t>
-  </si>
-  <si>
-    <t>If the amount of guaranteed dispatch exceeds demand in a given hour, then those sources marked with</t>
-  </si>
-  <si>
-    <t>0s will be scaled back proportionately while those with a value of 1 will not be reduced.</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -503,21 +506,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -525,30 +528,30 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1"/>
     </row>
   </sheetData>
@@ -563,15 +566,15 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AI25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" ht="30">
       <c r="A1" s="4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B1" s="2">
         <v>2021</v>
@@ -668,1054 +671,1054 @@
       <c r="AH1" s="2"/>
       <c r="AI1" s="2"/>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35">
       <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>1</v>
+      </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+      <c r="AB5">
+        <v>1</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>1</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6">
+        <v>1</v>
+      </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+      <c r="AB6">
+        <v>1</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>1</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+      <c r="W7">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>1</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+      <c r="AB7">
+        <v>1</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>1</v>
+      </c>
+      <c r="AE7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>1</v>
+      </c>
+      <c r="V8">
+        <v>1</v>
+      </c>
+      <c r="W8">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+      <c r="AB8">
+        <v>1</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>1</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>1</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+      <c r="W9">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>1</v>
+      </c>
+      <c r="Y9">
+        <v>1</v>
+      </c>
+      <c r="Z9">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9">
+        <v>1</v>
+      </c>
+      <c r="AC9">
+        <v>1</v>
+      </c>
+      <c r="AD9">
+        <v>1</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>1</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+      <c r="W10">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>1</v>
+      </c>
+      <c r="Y10">
+        <v>1</v>
+      </c>
+      <c r="Z10">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10">
+        <v>1</v>
+      </c>
+      <c r="AD10">
+        <v>1</v>
+      </c>
+      <c r="AE10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35">
+      <c r="A11" t="s">
         <v>17</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>1</v>
+      </c>
+      <c r="Y11">
+        <v>1</v>
+      </c>
+      <c r="Z11">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>1</v>
+      </c>
+      <c r="AB11">
+        <v>1</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11">
+        <v>1</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35">
+      <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="U5">
-        <v>1</v>
-      </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-      <c r="W5">
-        <v>1</v>
-      </c>
-      <c r="X5">
-        <v>1</v>
-      </c>
-      <c r="Y5">
-        <v>1</v>
-      </c>
-      <c r="Z5">
-        <v>1</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-      <c r="AB5">
-        <v>1</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <v>1</v>
-      </c>
-      <c r="AE5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="V7">
-        <v>1</v>
-      </c>
-      <c r="W7">
-        <v>1</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
-        <v>1</v>
-      </c>
-      <c r="Z7">
-        <v>1</v>
-      </c>
-      <c r="AA7">
-        <v>1</v>
-      </c>
-      <c r="AB7">
-        <v>1</v>
-      </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AD7">
-        <v>1</v>
-      </c>
-      <c r="AE7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-      <c r="U8">
-        <v>1</v>
-      </c>
-      <c r="V8">
-        <v>1</v>
-      </c>
-      <c r="W8">
-        <v>1</v>
-      </c>
-      <c r="X8">
-        <v>1</v>
-      </c>
-      <c r="Y8">
-        <v>1</v>
-      </c>
-      <c r="Z8">
-        <v>1</v>
-      </c>
-      <c r="AA8">
-        <v>1</v>
-      </c>
-      <c r="AB8">
-        <v>1</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AD8">
-        <v>1</v>
-      </c>
-      <c r="AE8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9">
-        <v>1</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
-      <c r="Q9">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9">
-        <v>1</v>
-      </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
-      <c r="U9">
-        <v>1</v>
-      </c>
-      <c r="V9">
-        <v>1</v>
-      </c>
-      <c r="W9">
-        <v>1</v>
-      </c>
-      <c r="X9">
-        <v>1</v>
-      </c>
-      <c r="Y9">
-        <v>1</v>
-      </c>
-      <c r="Z9">
-        <v>1</v>
-      </c>
-      <c r="AA9">
-        <v>1</v>
-      </c>
-      <c r="AB9">
-        <v>1</v>
-      </c>
-      <c r="AC9">
-        <v>1</v>
-      </c>
-      <c r="AD9">
-        <v>1</v>
-      </c>
-      <c r="AE9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>0</v>
-      </c>
-      <c r="V10">
-        <v>0</v>
-      </c>
-      <c r="W10">
-        <v>0</v>
-      </c>
-      <c r="X10">
-        <v>0</v>
-      </c>
-      <c r="Y10">
-        <v>0</v>
-      </c>
-      <c r="Z10">
-        <v>0</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0</v>
-      </c>
-      <c r="AC10">
-        <v>0</v>
-      </c>
-      <c r="AD10">
-        <v>0</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>1</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-      <c r="M11">
-        <v>1</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11">
-        <v>1</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-      <c r="U11">
-        <v>1</v>
-      </c>
-      <c r="V11">
-        <v>1</v>
-      </c>
-      <c r="W11">
-        <v>1</v>
-      </c>
-      <c r="X11">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>1</v>
-      </c>
-      <c r="Z11">
-        <v>1</v>
-      </c>
-      <c r="AA11">
-        <v>1</v>
-      </c>
-      <c r="AB11">
-        <v>1</v>
-      </c>
-      <c r="AC11">
-        <v>1</v>
-      </c>
-      <c r="AD11">
-        <v>1</v>
-      </c>
-      <c r="AE11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
       <c r="B12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1808,9 +1811,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1903,9 +1906,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -1998,9 +2001,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -2093,9 +2096,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2188,9 +2191,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2283,104 +2286,104 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2473,9 +2476,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2568,9 +2571,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2663,9 +2666,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2758,9 +2761,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31">
       <c r="A24" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2853,9 +2856,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31">
       <c r="A25" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2951,4 +2954,165 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7D38997-C871-49E6-8027-B42071D9793E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5E3D3FF-6E43-4588-A998-3E9D4A2AFAE6}"/>
 </file>